--- a/src/nodes/HPC/compressor_stage_3_blade_stator_coordinates_lattice.xlsx
+++ b/src/nodes/HPC/compressor_stage_3_blade_stator_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>4.7451520342484992</v>
+        <v>4.700794381635399</v>
       </c>
       <c r="B1">
-        <v>8.5795174310356561</v>
+        <v>8.6039014033845369</v>
       </c>
       <c r="C1">
         <v>194.11826296981104</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>4.1391265998079554</v>
+        <v>4.0957890406346928</v>
       </c>
       <c r="B2">
-        <v>8.3834968828450069</v>
+        <v>8.404754673904911</v>
       </c>
       <c r="C2">
         <v>194.11826296981104</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>3.6009222489870902</v>
+        <v>3.5588882960117258</v>
       </c>
       <c r="B3">
-        <v>8.1323868240595178</v>
+        <v>8.150869315349</v>
       </c>
       <c r="C3">
         <v>194.11826296981104</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>3.0810014697798831</v>
+        <v>3.0403475538929126</v>
       </c>
       <c r="B4">
-        <v>7.8664254394271822</v>
+        <v>7.88222722346865</v>
       </c>
       <c r="C4">
         <v>194.11826296981104</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>2.5763791623414449</v>
+        <v>2.5371692358080611</v>
       </c>
       <c r="B5">
-        <v>7.5880374570820095</v>
+        <v>7.6012376825814325</v>
       </c>
       <c r="C5">
         <v>194.11826296981104</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>2.0857141112141857</v>
+        <v>2.0480065196110222</v>
       </c>
       <c r="B6">
-        <v>7.2983123155764007</v>
+        <v>7.3089831922807758</v>
       </c>
       <c r="C6">
         <v>194.11826296981104</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>1.6081699957677609</v>
+        <v>1.5720195885968413</v>
       </c>
       <c r="B7">
-        <v>6.9979293389754851</v>
+        <v>7.0061387498142906</v>
       </c>
       <c r="C7">
         <v>194.11826296981104</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>1.1431849693731562</v>
+        <v>1.1086442474467031</v>
       </c>
       <c r="B8">
-        <v>6.6873449024087934</v>
+        <v>6.6931578235222347</v>
       </c>
       <c r="C8">
         <v>194.11826296981104</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>0.69001088785504039</v>
+        <v>0.6571292245150665</v>
       </c>
       <c r="B9">
-        <v>6.36716670622957</v>
+        <v>6.3706442431331105</v>
       </c>
       <c r="C9">
         <v>194.11826296981104</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>0.24786422193762409</v>
+        <v>0.216687715135451</v>
       </c>
       <c r="B10">
-        <v>6.0380311932965345</v>
+        <v>6.0392303978113056</v>
       </c>
       <c r="C10">
         <v>194.11826296981104</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-0.18399380051040831</v>
+        <v>-0.2134221411156747</v>
       </c>
       <c r="B11">
-        <v>5.7005384512665476</v>
+        <v>5.69951255307647</v>
       </c>
       <c r="C11">
         <v>194.11826296981104</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-0.60600896430392615</v>
+        <v>-0.6336479925692956</v>
       </c>
       <c r="B12">
-        <v>5.3550505809196469</v>
+        <v>5.3518505033808124</v>
       </c>
       <c r="C12">
         <v>194.11826296981104</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-1.0174998621364901</v>
+        <v>-1.043305583429174</v>
       </c>
       <c r="B13">
-        <v>5.0010140907304255</v>
+        <v>4.99569428255148</v>
       </c>
       <c r="C13">
         <v>194.11826296981104</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-1.418091694608151</v>
+        <v>-1.44201854751987</v>
       </c>
       <c r="B14">
-        <v>4.6381245397431758</v>
+        <v>4.6307413887079854</v>
       </c>
       <c r="C14">
         <v>194.11826296981104</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-1.8097632860662358</v>
+        <v>-1.8317739812763629</v>
       </c>
       <c r="B15">
-        <v>4.2679892815864306</v>
+        <v>4.2585889377643458</v>
       </c>
       <c r="C15">
         <v>194.11826296981104</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-2.1943288598895672</v>
+        <v>-2.2143936920830161</v>
       </c>
       <c r="B16">
-        <v>3.8920819682975112</v>
+        <v>3.8807011956286743</v>
       </c>
       <c r="C16">
         <v>194.11826296981104</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-2.5705906118357023</v>
+        <v>-2.5886748685113261</v>
       </c>
       <c r="B17">
-        <v>3.5094296509646119</v>
+        <v>3.4961114103908808</v>
       </c>
       <c r="C17">
         <v>194.11826296981104</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-2.9369760151773039</v>
+        <v>-2.9530384101939364</v>
       </c>
       <c r="B18">
-        <v>3.11875500219657</v>
+        <v>3.1035503903388051</v>
       </c>
       <c r="C18">
         <v>194.11826296981104</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-3.2934256808687525</v>
+        <v>-3.3074246798209512</v>
       </c>
       <c r="B19">
-        <v>2.720009781633848</v>
+        <v>2.7029702023701438</v>
       </c>
       <c r="C19">
         <v>194.11826296981104</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-3.6402585042848541</v>
+        <v>-3.65215390584684</v>
       </c>
       <c r="B20">
-        <v>2.3134530206748165</v>
+        <v>2.2946282280350578</v>
       </c>
       <c r="C20">
         <v>194.11826296981104</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-3.9777933808004184</v>
+        <v>-3.9875463167260721</v>
       </c>
       <c r="B21">
-        <v>1.8993437507178477</v>
+        <v>1.8787818488837103</v>
       </c>
       <c r="C21">
         <v>194.11826296981104</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-4.3062892667652655</v>
+        <v>-4.3138619513247782</v>
       </c>
       <c r="B22">
-        <v>1.477892316066155</v>
+        <v>1.4556400694737306</v>
       </c>
       <c r="C22">
         <v>194.11826296981104</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-4.6257653624292772</v>
+        <v>-4.6311200901557221</v>
       </c>
       <c r="B23">
-        <v>1.0491143126423135</v>
+        <v>1.0252183863926128</v>
       </c>
       <c r="C23">
         <v>194.11826296981104</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-4.9361809290173468</v>
+        <v>-4.9392798241433251</v>
       </c>
       <c r="B24">
-        <v>0.61297664927374274</v>
+        <v>0.58748391923532128</v>
       </c>
       <c r="C24">
         <v>194.11826296981104</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-5.2374952277543674</v>
+        <v>-5.238300244212013</v>
       </c>
       <c r="B25">
-        <v>0.16944623478785686</v>
+        <v>0.1424037875968143</v>
       </c>
       <c r="C25">
         <v>194.11826296981104</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-5.5296517511948791</v>
+        <v>-5.5281246066980136</v>
       </c>
       <c r="B26">
-        <v>-0.28152283051716043</v>
+        <v>-0.3100676158758367</v>
       </c>
       <c r="C26">
         <v>194.11826296981104</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-5.8125309172120092</v>
+        <v>-5.80863282958479</v>
       </c>
       <c r="B27">
-        <v>-0.74002768046008871</v>
+        <v>-0.77002680632715914</v>
       </c>
       <c r="C27">
         <v>194.11826296981104</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-6.085997375008529</v>
+        <v>-6.0796889962676168</v>
       </c>
       <c r="B28">
-        <v>-1.2061782573889412</v>
+        <v>-1.2375830258495717</v>
       </c>
       <c r="C28">
         <v>194.11826296981104</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-6.3499157737872034</v>
+        <v>-6.3411571901417565</v>
       </c>
       <c r="B29">
-        <v>-1.6800845036517311</v>
+        <v>-1.7128455165354899</v>
       </c>
       <c r="C29">
         <v>194.11826296981104</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-6.6041821283727762</v>
+        <v>-6.5929329913422894</v>
       </c>
       <c r="B30">
-        <v>-2.1618308840211884</v>
+        <v>-2.1958982051763236</v>
       </c>
       <c r="C30">
         <v>194.11826296981104</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-6.84881791607785</v>
+        <v>-6.8350379669635215</v>
       </c>
       <c r="B31">
-        <v>-2.6513999529689118</v>
+        <v>-2.6867237573594456</v>
       </c>
       <c r="C31">
         <v>194.11826296981104</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-7.0838759798370035</v>
+        <v>-7.0675251808395689</v>
       </c>
       <c r="B32">
-        <v>-3.1487487873912219</v>
+        <v>-3.1852795233712192</v>
       </c>
       <c r="C32">
         <v>194.11826296981104</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-7.309409162584811</v>
+        <v>-7.2904476968045451</v>
       </c>
       <c r="B33">
-        <v>-3.6538344641844378</v>
+        <v>-3.6915228534980082</v>
       </c>
       <c r="C33">
         <v>194.11826296981104</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-7.5253958856135865</v>
+        <v>-7.5037838459452013</v>
       </c>
       <c r="B34">
-        <v>-4.1666745112378463</v>
+        <v>-4.2054711639887481</v>
       </c>
       <c r="C34">
         <v>194.11826296981104</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-7.7315168836466164</v>
+        <v>-7.7072130283588614</v>
       </c>
       <c r="B35">
-        <v>-4.687528260412658</v>
+        <v>-4.7273821349427045</v>
       </c>
       <c r="C35">
         <v>194.11826296981104</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-7.927378469764931</v>
+        <v>-7.9003399113954877</v>
       </c>
       <c r="B36">
-        <v>-5.2167154945630569</v>
+        <v>-5.2575735124217111</v>
       </c>
       <c r="C36">
         <v>194.11826296981104</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-8.1125869570495563</v>
+        <v>-8.0827691624050448</v>
       </c>
       <c r="B37">
-        <v>-5.7545559965432256</v>
+        <v>-5.7963630424876094</v>
       </c>
       <c r="C37">
         <v>194.11826296981104</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-8.2865797409281168</v>
+        <v>-8.253935824956919</v>
       </c>
       <c r="B38">
-        <v>-6.3015067571427013</v>
+        <v>-6.34420480521934</v>
       </c>
       <c r="C38">
         <v>194.11826296981104</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-8.4481185462146247</v>
+        <v>-8.41259644749821</v>
       </c>
       <c r="B39">
-        <v>-6.8585735988924306</v>
+        <v>-6.9020982167642515</v>
       </c>
       <c r="C39">
         <v>194.11826296981104</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-8.5957961800696854</v>
+        <v>-8.5573379546954431</v>
       </c>
       <c r="B40">
-        <v>-7.4268995522587131</v>
+        <v>-7.4711790272867971</v>
       </c>
       <c r="C40">
         <v>194.11826296981104</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-8.7282054496539079</v>
+        <v>-8.68674727121514</v>
       </c>
       <c r="B41">
-        <v>-8.0076276477078512</v>
+        <v>-8.05258298695143</v>
       </c>
       <c r="C41">
         <v>194.11826296981104</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-8.7282054496539079</v>
+        <v>-8.68674727121514</v>
       </c>
       <c r="B42">
-        <v>-8.0076276477078512</v>
+        <v>-8.05258298695143</v>
       </c>
       <c r="C42">
         <v>194.11826296981104</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-8.5411969692007688</v>
+        <v>-8.50251050251814</v>
       </c>
       <c r="B43">
-        <v>-7.4712492388915637</v>
+        <v>-7.5152462375421125</v>
       </c>
       <c r="C43">
         <v>194.11826296981104</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-8.3482971071307457</v>
+        <v>-8.3123577244371685</v>
       </c>
       <c r="B44">
-        <v>-6.939656264230555</v>
+        <v>-6.9826644424311048</v>
       </c>
       <c r="C44">
         <v>194.11826296981104</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-8.14860219743282</v>
+        <v>-8.1153814933624222</v>
       </c>
       <c r="B45">
-        <v>-6.4135827508979579</v>
+        <v>-6.4555669535536193</v>
       </c>
       <c r="C45">
         <v>194.11826296981104</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-7.9412085740959775</v>
+        <v>-7.9106743656840939</v>
       </c>
       <c r="B46">
-        <v>-5.893762726066905</v>
+        <v>-5.9346831228448611</v>
       </c>
       <c r="C46">
         <v>194.11826296981104</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-7.725356248571682</v>
+        <v>-7.6974731758703632</v>
       </c>
       <c r="B47">
-        <v>-5.3808135110033177</v>
+        <v>-5.4206263396675478</v>
       </c>
       <c r="C47">
         <v>194.11826296981104</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-7.50085994216136</v>
+        <v>-7.4755918707013409</v>
       </c>
       <c r="B48">
-        <v>-4.8748856033442625</v>
+        <v>-4.9135461430944245</v>
       </c>
       <c r="C48">
         <v>194.11826296981104</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-7.2676780536289272</v>
+        <v>-7.2449886750351222</v>
       </c>
       <c r="B49">
-        <v>-4.3760127948195953</v>
+        <v>-4.4134761096257424</v>
       </c>
       <c r="C49">
         <v>194.11826296981104</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-7.025768981738298</v>
+        <v>-7.0056218137298005</v>
       </c>
       <c r="B50">
-        <v>-3.8842288771591682</v>
+        <v>-3.9204498157617529</v>
       </c>
       <c r="C50">
         <v>194.11826296981104</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-6.7751441239864736</v>
+        <v>-6.75750273192738</v>
       </c>
       <c r="B51">
-        <v>-3.3995245924375914</v>
+        <v>-3.43445806254355</v>
       </c>
       <c r="C51">
         <v>194.11826296981104</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-6.5160268728028257</v>
+        <v>-6.5008557559055378</v>
       </c>
       <c r="B52">
-        <v>-2.9217184841085033</v>
+        <v>-2.9553205491756223</v>
       </c>
       <c r="C52">
         <v>194.11826296981104</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-6.2486936193498108</v>
+        <v>-6.2359584322258534</v>
       </c>
       <c r="B53">
-        <v>-2.4505860459702928</v>
+        <v>-2.4828141994032942</v>
       </c>
       <c r="C53">
         <v>194.11826296981104</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-5.9734207547898839</v>
+        <v>-5.9630883074499108</v>
       </c>
       <c r="B54">
-        <v>-1.9859027718213476</v>
+        <v>-2.0167159369718912</v>
       </c>
       <c r="C54">
         <v>194.11826296981104</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-5.6904370707290273</v>
+        <v>-5.682475129602194</v>
       </c>
       <c r="B55">
-        <v>-1.527482819487981</v>
+        <v>-1.5568411033919423</v>
       </c>
       <c r="C55">
         <v>194.11826296981104</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-5.3997809605473117</v>
+        <v>-5.3941574525587788</v>
       </c>
       <c r="B56">
-        <v>-1.0752950029081998</v>
+        <v>-1.1031587112347803</v>
       </c>
       <c r="C56">
         <v>194.11826296981104</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-5.1014432180683356</v>
+        <v>-5.0981260316586479</v>
       </c>
       <c r="B57">
-        <v>-0.62934680004793309</v>
+        <v>-0.6556761908369404</v>
       </c>
       <c r="C57">
         <v>194.11826296981104</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-4.7954146371156945</v>
+        <v>-4.794371622240778</v>
       </c>
       <c r="B58">
-        <v>-0.18964568887311004</v>
+        <v>-0.21440097253495838</v>
       </c>
       <c r="C58">
         <v>194.11826296981104</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-4.4816876282474327</v>
+        <v>-4.4828866031370378</v>
       </c>
       <c r="B59">
-        <v>0.24380216588665379</v>
+        <v>0.22066081820655387</v>
       </c>
       <c r="C59">
         <v>194.11826296981104</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-4.1602610689593993</v>
+        <v>-4.1636698471508682</v>
       </c>
       <c r="B60">
-        <v>0.67099585244698035</v>
+        <v>0.64950827541064271</v>
       </c>
       <c r="C60">
         <v>194.11826296981104</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-3.8311354534818887</v>
+        <v>-3.8367218505785985</v>
       </c>
       <c r="B61">
-        <v>1.0919357722598049</v>
+        <v>1.0721417979722769</v>
       </c>
       <c r="C61">
         <v>194.11826296981104</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-3.4943112760452033</v>
+        <v>-3.5020431097165603</v>
       </c>
       <c r="B62">
-        <v>1.5066223267770607</v>
+        <v>1.4885617847864232</v>
       </c>
       <c r="C62">
         <v>194.11826296981104</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-3.1498349281946494</v>
+        <v>-3.1596802100408325</v>
       </c>
       <c r="B63">
-        <v>1.9150931987869089</v>
+        <v>1.8988056786283287</v>
       </c>
       <c r="C63">
         <v>194.11826296981104</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-2.7979363907355852</v>
+        <v>-2.8098640937464889</v>
       </c>
       <c r="B64">
-        <v>2.3175351964224125</v>
+        <v>2.3030590977943581</v>
       </c>
       <c r="C64">
         <v>194.11826296981104</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.438891541788379</v>
+        <v>-2.4528717922083536</v>
       </c>
       <c r="B65">
-        <v>2.71417240915286</v>
+        <v>2.7015447044611558</v>
       </c>
       <c r="C65">
         <v>194.11826296981104</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.0729762594733971</v>
+        <v>-2.0889803368012472</v>
       </c>
       <c r="B66">
-        <v>3.10522892644754</v>
+        <v>3.0944851608053643</v>
       </c>
       <c r="C66">
         <v>194.11826296981104</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.7000764831850814</v>
+        <v>-1.7180751901115878</v>
       </c>
       <c r="B67">
-        <v>3.4906120994927958</v>
+        <v>3.4817884081212465</v>
       </c>
       <c r="C67">
         <v>194.11826296981104</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-1.3185183974141681</v>
+        <v>-1.3384755395721728</v>
       </c>
       <c r="B68">
-        <v>3.8689623263431776</v>
+        <v>3.8621035041735245</v>
       </c>
       <c r="C68">
         <v>194.11826296981104</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-0.92698554777982345</v>
+        <v>-0.94885942762244335</v>
       </c>
       <c r="B69">
-        <v>4.23921028130099</v>
+        <v>4.234367934118703</v>
       </c>
       <c r="C69">
         <v>194.11826296981104</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-0.52715067931867476</v>
+        <v>-0.55090659188206237</v>
       </c>
       <c r="B70">
-        <v>4.6027146967913026</v>
+        <v>4.599931776209913</v>
       </c>
       <c r="C70">
         <v>194.11826296981104</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-0.12083674082275039</v>
+        <v>-0.14644760162348028</v>
       </c>
       <c r="B71">
-        <v>4.9609563123044449</v>
+        <v>4.9602663386661723</v>
       </c>
       <c r="C71">
         <v>194.11826296981104</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>0.29252170331173527</v>
+        <v>0.2650853424498974</v>
       </c>
       <c r="B72">
-        <v>5.3134758374689985</v>
+        <v>5.31491525647338</v>
       </c>
       <c r="C72">
         <v>194.11826296981104</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>0.71381439893719811</v>
+        <v>0.684585705598774</v>
       </c>
       <c r="B73">
-        <v>5.6595505521373743</v>
+        <v>5.6631604127040536</v>
       </c>
       <c r="C73">
         <v>194.11826296981104</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>1.142839948504738</v>
+        <v>1.1118512483712382</v>
       </c>
       <c r="B74">
-        <v>5.9993440469190347</v>
+        <v>6.0051643560102912</v>
       </c>
       <c r="C74">
         <v>194.11826296981104</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>1.5791232012481349</v>
+        <v>1.5464048337263456</v>
       </c>
       <c r="B75">
-        <v>6.33324227588273</v>
+        <v>6.3413105822042981</v>
       </c>
       <c r="C75">
         <v>194.11826296981104</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>2.0221851369331989</v>
+        <v>1.9877654389796273</v>
       </c>
       <c r="B76">
-        <v>6.66163433617728</v>
+        <v>6.6719857101591415</v>
       </c>
       <c r="C76">
         <v>194.11826296981104</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>2.4716047897129076</v>
+        <v>2.4355103385187791</v>
       </c>
       <c r="B77">
-        <v>6.9848621687044252</v>
+        <v>6.9975295028530029</v>
       </c>
       <c r="C77">
         <v>194.11826296981104</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>2.9271972807568702</v>
+        <v>2.8894538806636665</v>
       </c>
       <c r="B78">
-        <v>7.3030759462974739</v>
+        <v>7.3180911766236445</v>
       </c>
       <c r="C78">
         <v>194.11826296981104</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>3.388527139539788</v>
+        <v>3.3491587744897413</v>
       </c>
       <c r="B79">
-        <v>7.6166293916756311</v>
+        <v>7.6340222012248011</v>
       </c>
       <c r="C79">
         <v>194.11826296981104</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>3.8547055686918661</v>
+        <v>3.8137325071838664</v>
       </c>
       <c r="B80">
-        <v>7.9262444545558122</v>
+        <v>7.9460399280603857</v>
       </c>
       <c r="C80">
         <v>194.11826296981104</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>4.3232439101820086</v>
+        <v>4.2806760173674228</v>
       </c>
       <c r="B81">
-        <v>8.2339426147736887</v>
+        <v>8.2561529615582714</v>
       </c>
       <c r="C81">
         <v>194.11826296981104</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>4.7451520342484992</v>
+        <v>4.700794381635399</v>
       </c>
       <c r="B82">
-        <v>8.5795174310356561</v>
+        <v>8.6039014033845369</v>
       </c>
       <c r="C82">
         <v>194.11826296981104</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>4.7714476386357711</v>
+        <v>4.751242071460017</v>
       </c>
       <c r="B1">
-        <v>9.74396643132508</v>
+        <v>9.7538347926044615</v>
       </c>
       <c r="C1">
         <v>228.43351223002802</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>4.0448888780669048</v>
+        <v>3.98968796282698</v>
       </c>
       <c r="B2">
-        <v>9.5418010139920035</v>
+        <v>9.5758775048600615</v>
       </c>
       <c r="C2">
         <v>228.43351223002802</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>3.4402331715742558</v>
+        <v>3.3722361861986396</v>
       </c>
       <c r="B3">
-        <v>9.250742034461414</v>
+        <v>9.2932953974707626</v>
       </c>
       <c r="C3">
         <v>228.43351223002802</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>2.8625603825602415</v>
+        <v>2.7848710484021471</v>
       </c>
       <c r="B4">
-        <v>8.9400067008695228</v>
+        <v>8.98886902762081</v>
       </c>
       <c r="C4">
         <v>228.43351223002802</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>2.3063402242125437</v>
+        <v>2.2210010105826883</v>
       </c>
       <c r="B5">
-        <v>8.6136277825218</v>
+        <v>8.6673841510594158</v>
       </c>
       <c r="C5">
         <v>228.43351223002802</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>1.7691814846173453</v>
+        <v>1.6778022974663849</v>
       </c>
       <c r="B6">
-        <v>8.27334898753613</v>
+        <v>8.3308909565284122</v>
       </c>
       <c r="C6">
         <v>228.43351223002802</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>1.2496413613353332</v>
+        <v>1.1535852935042763</v>
       </c>
       <c r="B7">
-        <v>7.9202224294083559</v>
+        <v>7.9806161814415519</v>
       </c>
       <c r="C7">
         <v>228.43351223002802</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>0.74679437320798048</v>
+        <v>0.64727948428069859</v>
       </c>
       <c r="B8">
-        <v>7.5549229830835865</v>
+        <v>7.6173370677498005</v>
       </c>
       <c r="C8">
         <v>228.43351223002802</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>0.25933673320383294</v>
+        <v>0.15735423070622862</v>
       </c>
       <c r="B9">
-        <v>7.1784013899066625</v>
+        <v>7.242164928757008</v>
       </c>
       <c r="C9">
         <v>228.43351223002802</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-0.21411261833429546</v>
+        <v>-0.31781646912411571</v>
       </c>
       <c r="B10">
-        <v>6.791664739597076</v>
+        <v>6.85628031549024</v>
       </c>
       <c r="C10">
         <v>228.43351223002802</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-0.67486552569359126</v>
+        <v>-0.77977994370379256</v>
       </c>
       <c r="B11">
-        <v>6.3956696489731648</v>
+        <v>6.4608066585165611</v>
       </c>
       <c r="C11">
         <v>228.43351223002802</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-1.123678971982111</v>
+        <v>-1.2294188074682415</v>
       </c>
       <c r="B12">
-        <v>5.9909681216373709</v>
+        <v>6.0563847758910248</v>
       </c>
       <c r="C12">
         <v>228.43351223002802</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-1.5591597109613966</v>
+        <v>-1.6650354920323502</v>
       </c>
       <c r="B13">
-        <v>5.5765441812296812</v>
+        <v>5.6417821560806365</v>
       </c>
       <c r="C13">
         <v>228.43351223002802</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-1.9805105969011183</v>
+        <v>-2.0856507895344265</v>
       </c>
       <c r="B14">
-        <v>5.1518165369522864</v>
+        <v>5.2162878498280261</v>
       </c>
       <c r="C14">
         <v>228.43351223002802</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-2.3914691154499903</v>
+        <v>-2.4957391170270253</v>
       </c>
       <c r="B15">
-        <v>4.719510620218645</v>
+        <v>4.783150486566365</v>
       </c>
       <c r="C15">
         <v>228.43351223002802</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-2.7954624631287035</v>
+        <v>-2.8994035798241597</v>
       </c>
       <c r="B16">
-        <v>4.2821255948879733</v>
+        <v>4.3453491065893859</v>
       </c>
       <c r="C16">
         <v>228.43351223002802</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-3.1901420485668126</v>
+        <v>-3.293808411371455</v>
       </c>
       <c r="B17">
-        <v>3.8379488323912234</v>
+        <v>3.9008248149425175</v>
       </c>
       <c r="C17">
         <v>228.43351223002802</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-3.572446604728821</v>
+        <v>-3.6752632737977708</v>
       </c>
       <c r="B18">
-        <v>3.3847480102186314</v>
+        <v>3.4468982591904056</v>
       </c>
       <c r="C18">
         <v>228.43351223002802</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-3.942239949810157</v>
+        <v>-4.0435984158332774</v>
       </c>
       <c r="B19">
-        <v>2.9224238225258428</v>
+        <v>2.98344619222287</v>
       </c>
       <c r="C19">
         <v>228.43351223002802</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-4.3001171733139856</v>
+        <v>-4.39952423285848</v>
       </c>
       <c r="B20">
-        <v>2.4514102176348462</v>
+        <v>2.510984393261015</v>
       </c>
       <c r="C20">
         <v>228.43351223002802</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-4.6466733647434619</v>
+        <v>-4.7437511202538722</v>
       </c>
       <c r="B21">
-        <v>1.9721411438676424</v>
+        <v>2.0300286415259547</v>
       </c>
       <c r="C21">
         <v>228.43351223002802</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-4.9823941701271632</v>
+        <v>-5.0768595065839843</v>
       </c>
       <c r="B22">
-        <v>1.484970741699</v>
+        <v>1.5410003544440076</v>
       </c>
       <c r="C22">
         <v>228.43351223002802</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-5.3073274615952952</v>
+        <v>-5.3989099531494418</v>
       </c>
       <c r="B23">
-        <v>0.98993392021480464</v>
+        <v>1.0439435022623396</v>
       </c>
       <c r="C23">
         <v>228.43351223002802</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-5.6214116678034856</v>
+        <v>-5.7098330544348954</v>
       </c>
       <c r="B24">
-        <v>0.48698578065372061</v>
+        <v>0.53880769343332691</v>
       </c>
       <c r="C24">
         <v>228.43351223002802</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-5.9245852174073512</v>
+        <v>-6.0095594049249961</v>
       </c>
       <c r="B25">
-        <v>-0.023918575745587</v>
+        <v>0.025542536409351325</v>
       </c>
       <c r="C25">
         <v>228.43351223002802</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-6.2167619850183726</v>
+        <v>-6.2979916638303006</v>
       </c>
       <c r="B26">
-        <v>-0.54284195292711057</v>
+        <v>-0.49592264263143093</v>
       </c>
       <c r="C26">
         <v>228.43351223002802</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-6.4977576290714785</v>
+        <v>-6.5749207492650141</v>
       </c>
       <c r="B27">
-        <v>-1.0699187755654886</v>
+        <v>-1.0257396466077482</v>
       </c>
       <c r="C27">
         <v>228.43351223002802</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-6.7673632539574475</v>
+        <v>-6.8401096440692379</v>
       </c>
       <c r="B28">
-        <v>-1.6053013735180046</v>
+        <v>-1.5640805607125365</v>
       </c>
       <c r="C28">
         <v>228.43351223002802</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-7.0253699640670675</v>
+        <v>-7.093321331083084</v>
       </c>
       <c r="B29">
-        <v>-2.149142076641954</v>
+        <v>-2.1111174701387423</v>
       </c>
       <c r="C29">
         <v>228.43351223002802</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-7.271635708995543</v>
+        <v>-7.3344009285954446</v>
       </c>
       <c r="B30">
-        <v>-2.7015444702542837</v>
+        <v>-2.6669628260234512</v>
       </c>
       <c r="C30">
         <v>228.43351223002802</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-7.5062858191557549</v>
+        <v>-7.563522096690364</v>
       </c>
       <c r="B31">
-        <v>-3.2624171615105935</v>
+        <v>-3.2314905432803185</v>
       </c>
       <c r="C31">
         <v>228.43351223002802</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-7.7295124701650115</v>
+        <v>-7.780940630900675</v>
       </c>
       <c r="B32">
-        <v>-3.8316200130261469</v>
+        <v>-3.8045149027671497</v>
       </c>
       <c r="C32">
         <v>228.43351223002802</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-7.9415078376406205</v>
+        <v>-7.9869123267592137</v>
       </c>
       <c r="B33">
-        <v>-4.4090128874162087</v>
+        <v>-4.3858501853417478</v>
       </c>
       <c r="C33">
         <v>228.43351223002802</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-8.14232993946973</v>
+        <v>-8.1815341096272416</v>
       </c>
       <c r="B34">
-        <v>-4.9945534771545264</v>
+        <v>-4.9754260188019384</v>
       </c>
       <c r="C34">
         <v>228.43351223002802</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-8.3315001626188749</v>
+        <v>-8.3642674241797543</v>
       </c>
       <c r="B35">
-        <v>-5.5885907941488187</v>
+        <v>-5.5736334187056533</v>
       </c>
       <c r="C35">
         <v>228.43351223002802</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-8.5084057363244234</v>
+        <v>-8.53441484492017</v>
       </c>
       <c r="B36">
-        <v>-6.1915716801652829</v>
+        <v>-6.1809787475508449</v>
       </c>
       <c r="C36">
         <v>228.43351223002802</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-8.672433889822754</v>
+        <v>-8.6912789463519111</v>
       </c>
       <c r="B37">
-        <v>-6.8039429769701307</v>
+        <v>-6.7979683678354714</v>
       </c>
       <c r="C37">
         <v>228.43351223002802</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-8.8226578528525</v>
+        <v>-8.8337877002999061</v>
       </c>
       <c r="B38">
-        <v>-7.4263804995418772</v>
+        <v>-7.4253806205683954</v>
       </c>
       <c r="C38">
         <v>228.43351223002802</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-8.95689485716134</v>
+        <v>-8.9593706678750546</v>
       </c>
       <c r="B39">
-        <v>-8.0604759557082772</v>
+        <v>-8.0650817608021086</v>
       </c>
       <c r="C39">
         <v>228.43351223002802</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-9.07264813499921</v>
+        <v>-9.06508280750976</v>
       </c>
       <c r="B40">
-        <v>-8.7080500265093956</v>
+        <v>-8.7192100221000075</v>
       </c>
       <c r="C40">
         <v>228.43351223002802</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-9.1674209186160471</v>
+        <v>-9.1479790776364283</v>
       </c>
       <c r="B41">
-        <v>-9.3709233929853042</v>
+        <v>-9.3899036380254923</v>
       </c>
       <c r="C41">
         <v>228.43351223002802</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-9.1674209186160471</v>
+        <v>-9.1479790776364283</v>
       </c>
       <c r="B42">
-        <v>-9.3709233929853042</v>
+        <v>-9.3899036380254923</v>
       </c>
       <c r="C42">
         <v>228.43351223002802</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-8.9677819976682489</v>
+        <v>-8.9390535232138362</v>
       </c>
       <c r="B43">
-        <v>-8.7845200097422556</v>
+        <v>-8.81071299055306</v>
       </c>
       <c r="C43">
         <v>228.43351223002802</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-8.7651725122235078</v>
+        <v>-8.7289566321239924</v>
       </c>
       <c r="B44">
-        <v>-8.2002828073375138</v>
+        <v>-8.2323727865526344</v>
       </c>
       <c r="C44">
         <v>228.43351223002802</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-8.5576508720830553</v>
+        <v>-8.5152993782366035</v>
       </c>
       <c r="B45">
-        <v>-7.61962762289184</v>
+        <v>-7.6566175671973618</v>
       </c>
       <c r="C45">
         <v>228.43351223002802</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-8.3432754870481283</v>
+        <v>-8.2956927354213743</v>
       </c>
       <c r="B46">
-        <v>-7.0439702935260078</v>
+        <v>-7.0851818736604</v>
       </c>
       <c r="C46">
         <v>228.43351223002802</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-8.12039115416464</v>
+        <v>-8.06809462630044</v>
       </c>
       <c r="B47">
-        <v>-6.4745178184236192</v>
+        <v>-6.5195483466068085</v>
       </c>
       <c r="C47">
         <v>228.43351223002802</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-7.8884882194572192</v>
+        <v>-7.8318507685056531</v>
       </c>
       <c r="B48">
-        <v>-5.9116418450196191</v>
+        <v>-5.9601920246692828</v>
       </c>
       <c r="C48">
         <v>228.43351223002802</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-7.6473434161951612</v>
+        <v>-7.5866538284212988</v>
       </c>
       <c r="B49">
-        <v>-5.35550518281178</v>
+        <v>-5.4073360459724249</v>
       </c>
       <c r="C49">
         <v>228.43351223002802</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-7.3967334776477749</v>
+        <v>-7.33219647243167</v>
       </c>
       <c r="B50">
-        <v>-4.8062706412978864</v>
+        <v>-4.8612035486408463</v>
       </c>
       <c r="C50">
         <v>228.43351223002802</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-7.1365457096784617</v>
+        <v>-7.06830661636136</v>
       </c>
       <c r="B51">
-        <v>-4.2640203987573591</v>
+        <v>-4.3219194735798316</v>
       </c>
       <c r="C51">
         <v>228.43351223002802</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-6.8671097085270283</v>
+        <v>-6.7953531737962338</v>
       </c>
       <c r="B52">
-        <v>-3.7285141085962246</v>
+        <v>-3.7892159728174053</v>
       </c>
       <c r="C52">
         <v>228.43351223002802</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-6.5888656430273755</v>
+        <v>-6.5138403077624583</v>
       </c>
       <c r="B53">
-        <v>-3.1994307930021457</v>
+        <v>-3.2627270011622693</v>
       </c>
       <c r="C53">
         <v>228.43351223002802</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-6.302253682013407</v>
+        <v>-6.2242721812862056</v>
       </c>
       <c r="B54">
-        <v>-2.6764494741627898</v>
+        <v>-2.742086513423124</v>
       </c>
       <c r="C54">
         <v>228.43351223002802</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-6.0076291748177617</v>
+        <v>-5.9270528205208208</v>
       </c>
       <c r="B55">
-        <v>-2.1593110259369608</v>
+        <v>-2.2270011683137017</v>
       </c>
       <c r="C55">
         <v>228.43351223002802</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-5.7050081927680187</v>
+        <v>-5.6221857041283183</v>
       </c>
       <c r="B56">
-        <v>-1.6480037288680149</v>
+        <v>-1.7174684401678242</v>
       </c>
       <c r="C56">
         <v>228.43351223002802</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-5.3943219876904873</v>
+        <v>-5.30957417389788</v>
       </c>
       <c r="B57">
-        <v>-1.1425777151704337</v>
+        <v>-1.2135585072243347</v>
       </c>
       <c r="C57">
         <v>228.43351223002802</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-5.0755018114114847</v>
+        <v>-4.9891215716186972</v>
       </c>
       <c r="B58">
-        <v>-0.64308311705871213</v>
+        <v>-0.715341547722086</v>
       </c>
       <c r="C58">
         <v>228.43351223002802</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-4.7484877530428085</v>
+        <v>-4.660743433875318</v>
       </c>
       <c r="B59">
-        <v>-0.14956362246426211</v>
+        <v>-0.22287888592615809</v>
       </c>
       <c r="C59">
         <v>228.43351223002802</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-4.413255250838235</v>
+        <v>-4.3244040764337814</v>
       </c>
       <c r="B60">
-        <v>0.33796285781377816</v>
+        <v>0.26380356979339903</v>
       </c>
       <c r="C60">
         <v>228.43351223002802</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-4.0697885803370326</v>
+        <v>-3.9800800098554969</v>
       </c>
       <c r="B61">
-        <v>0.8194848572593374</v>
+        <v>0.74468876504029069</v>
       </c>
       <c r="C61">
         <v>228.43351223002802</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-3.7180720170784638</v>
+        <v>-3.6277477447018684</v>
       </c>
       <c r="B62">
-        <v>1.2949909093563492</v>
+        <v>1.2197596454182289</v>
       </c>
       <c r="C62">
         <v>228.43351223002802</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-3.3581836680095378</v>
+        <v>-3.26749812272136</v>
       </c>
       <c r="B63">
-        <v>1.7645379708792295</v>
+        <v>1.6890821661509536</v>
       </c>
       <c r="C63">
         <v>228.43351223002802</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-2.990576965708224</v>
+        <v>-2.8998793104106584</v>
       </c>
       <c r="B64">
-        <v>2.2284566917643422</v>
+        <v>2.1530543209423434</v>
       </c>
       <c r="C64">
         <v>228.43351223002802</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.6157991741602391</v>
+        <v>-2.52555380545351</v>
       </c>
       <c r="B65">
-        <v>2.6871461452385264</v>
+        <v>2.6121571131162988</v>
       </c>
       <c r="C65">
         <v>228.43351223002802</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.234397557351294</v>
+        <v>-2.1451841055336573</v>
       </c>
       <c r="B66">
-        <v>3.1410054045286326</v>
+        <v>3.0668715459967304</v>
       </c>
       <c r="C66">
         <v>228.43351223002802</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.8461751604956842</v>
+        <v>-1.7585395946802382</v>
       </c>
       <c r="B67">
-        <v>3.5898908472075926</v>
+        <v>3.517030181943849</v>
       </c>
       <c r="C67">
         <v>228.43351223002802</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-1.4479581537220299</v>
+        <v>-1.3618172023039525</v>
       </c>
       <c r="B68">
-        <v>4.0314880682326955</v>
+        <v>3.9598718194630846</v>
       </c>
       <c r="C68">
         <v>228.43351223002802</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-1.0372661100710607</v>
+        <v>-0.95204912729247249</v>
       </c>
       <c r="B69">
-        <v>4.4639883025171994</v>
+        <v>4.3932417005307505</v>
       </c>
       <c r="C69">
         <v>228.43351223002802</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-0.617369089317624</v>
+        <v>-0.53318110105978489</v>
       </c>
       <c r="B70">
-        <v>4.8897761274138842</v>
+        <v>4.8200046048614587</v>
       </c>
       <c r="C70">
         <v>228.43351223002802</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-0.19183149274118852</v>
+        <v>-0.10951419506651092</v>
       </c>
       <c r="B71">
-        <v>5.3114507585801007</v>
+        <v>5.2432833051375622</v>
       </c>
       <c r="C71">
         <v>228.43351223002802</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>0.2403553990943906</v>
+        <v>0.3201426915664814</v>
       </c>
       <c r="B72">
-        <v>5.728276622451947</v>
+        <v>5.6622130081740751</v>
       </c>
       <c r="C72">
         <v>228.43351223002802</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>0.6808159799550112</v>
+        <v>0.75771862360460551</v>
       </c>
       <c r="B73">
-        <v>6.1390691863747175</v>
+        <v>6.0753931255810887</v>
       </c>
       <c r="C73">
         <v>228.43351223002802</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>1.1290642202099552</v>
+        <v>1.2026023490186244</v>
       </c>
       <c r="B74">
-        <v>6.5441828705517047</v>
+        <v>6.4832674540163406</v>
       </c>
       <c r="C74">
         <v>228.43351223002802</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>1.5840804395097652</v>
+        <v>1.6535391441929621</v>
       </c>
       <c r="B75">
-        <v>6.9443612414116043</v>
+        <v>6.8867469796530489</v>
       </c>
       <c r="C75">
         <v>228.43351223002802</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>2.044820778026645</v>
+        <v>2.1092407159613238</v>
       </c>
       <c r="B76">
-        <v>7.34036549742668</v>
+        <v>7.2867670616786571</v>
       </c>
       <c r="C76">
         <v>228.43351223002802</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>2.5103435681378885</v>
+        <v>2.5685390911614987</v>
       </c>
       <c r="B77">
-        <v>7.7328823169580554</v>
+        <v>7.68417570150818</v>
       </c>
       <c r="C77">
         <v>228.43351223002802</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>2.9801400905194844</v>
+        <v>3.0307811461983354</v>
       </c>
       <c r="B78">
-        <v>8.1222826658786733</v>
+        <v>8.0794470964526361</v>
       </c>
       <c r="C78">
         <v>228.43351223002802</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>3.4532104781314321</v>
+        <v>3.494720869409905</v>
       </c>
       <c r="B79">
-        <v>8.509295662450441</v>
+        <v>8.4734859074123126</v>
       </c>
       <c r="C79">
         <v>228.43351223002802</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>3.9276628620941705</v>
+        <v>3.958034582175916</v>
       </c>
       <c r="B80">
-        <v>8.8953008862514924</v>
+        <v>8.8679792303084124</v>
       </c>
       <c r="C80">
         <v>228.43351223002802</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>4.3985143398166473</v>
+        <v>4.4146789559869646</v>
       </c>
       <c r="B81">
-        <v>9.2839319456828431</v>
+        <v>9.26731479535012</v>
       </c>
       <c r="C81">
         <v>228.43351223002802</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>4.7714476386357711</v>
+        <v>4.751242071460017</v>
       </c>
       <c r="B82">
-        <v>9.74396643132508</v>
+        <v>9.7538347926044615</v>
       </c>
       <c r="C82">
         <v>228.43351223002802</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>4.79113733979563</v>
+        <v>4.78565604483323</v>
       </c>
       <c r="B1">
-        <v>10.732764606508106</v>
+        <v>10.735209794319259</v>
       </c>
       <c r="C1">
         <v>258.22826917492205</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>3.9385388418480045</v>
+        <v>3.8543574754654166</v>
       </c>
       <c r="B2">
-        <v>10.532995447324929</v>
+        <v>10.587851477299322</v>
       </c>
       <c r="C2">
         <v>258.22826917492205</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>3.2703369370559066</v>
+        <v>3.1565038394759153</v>
       </c>
       <c r="B3">
-        <v>10.209430000923577</v>
+        <v>10.283940714067818</v>
       </c>
       <c r="C3">
         <v>258.22826917492205</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>2.6386738832328795</v>
+        <v>2.5020169011692115</v>
       </c>
       <c r="B4">
-        <v>9.8613338730612377</v>
+        <v>9.95094744941677</v>
       </c>
       <c r="C4">
         <v>258.22826917492205</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>2.0350672986537921</v>
+        <v>1.8800686039828871</v>
       </c>
       <c r="B5">
-        <v>9.4944017858928547</v>
+        <v>9.59613317631599</v>
       </c>
       <c r="C5">
         <v>258.22826917492205</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>1.4559169476267209</v>
+        <v>1.2861030331160488</v>
       </c>
       <c r="B6">
-        <v>9.1110507895609683</v>
+        <v>9.2225531746402183</v>
       </c>
       <c r="C6">
         <v>258.22826917492205</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>0.89908659827483317</v>
+        <v>0.71743889809450279</v>
       </c>
       <c r="B7">
-        <v>8.7127150622706271</v>
+        <v>8.8320055668702668</v>
       </c>
       <c r="C7">
         <v>258.22826917492205</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>0.36323982825292933</v>
+        <v>0.17241972014566537</v>
       </c>
       <c r="B8">
-        <v>8.3002918230086866</v>
+        <v>8.4256012179976842</v>
       </c>
       <c r="C8">
         <v>258.22826917492205</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-0.15356399475832541</v>
+        <v>-0.35139617709858356</v>
       </c>
       <c r="B9">
-        <v>7.8750839324835749</v>
+        <v>8.00497756089692</v>
       </c>
       <c r="C9">
         <v>258.22826917492205</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-0.65339248812616491</v>
+        <v>-0.85661749066516</v>
       </c>
       <c r="B10">
-        <v>7.43847950394115</v>
+        <v>7.5718840355540058</v>
       </c>
       <c r="C10">
         <v>258.22826917492205</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-1.1382169994352587</v>
+        <v>-1.3457358026206439</v>
       </c>
       <c r="B11">
-        <v>6.9918020190554673</v>
+        <v>7.1279915425184415</v>
       </c>
       <c r="C11">
         <v>258.22826917492205</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-1.6091491257914548</v>
+        <v>-1.8201400850139737</v>
       </c>
       <c r="B12">
-        <v>6.5357977583961988</v>
+        <v>6.6742315518754136</v>
       </c>
       <c r="C12">
         <v>258.22826917492205</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-2.0639577321678506</v>
+        <v>-2.2769259847838565</v>
       </c>
       <c r="B13">
-        <v>6.0689688296873214</v>
+        <v>6.2086563512893953</v>
       </c>
       <c r="C13">
         <v>258.22826917492205</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-2.501346224596996</v>
+        <v>-2.7143940431147593</v>
       </c>
       <c r="B14">
-        <v>5.5904447530764</v>
+        <v>5.73012625256516</v>
       </c>
       <c r="C14">
         <v>258.22826917492205</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-2.9270989054819969</v>
+        <v>-3.1399577032844084</v>
       </c>
       <c r="B15">
-        <v>5.1041088712510447</v>
+        <v>5.2436128464893743</v>
       </c>
       <c r="C15">
         <v>258.22826917492205</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-3.346520288381889</v>
+        <v>-3.560415718906627</v>
       </c>
       <c r="B16">
-        <v>4.613522416405794</v>
+        <v>4.75367550170642</v>
       </c>
       <c r="C16">
         <v>258.22826917492205</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-3.7559148351089156</v>
+        <v>-3.9709951828463557</v>
       </c>
       <c r="B17">
-        <v>4.1162043562228066</v>
+        <v>4.2571134193095821</v>
       </c>
       <c r="C17">
         <v>258.22826917492205</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-4.150480571360748</v>
+        <v>-4.365503040951376</v>
       </c>
       <c r="B18">
-        <v>3.6089308426918132</v>
+        <v>3.7497734238025284</v>
       </c>
       <c r="C18">
         <v>258.22826917492205</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-4.5299898301235739</v>
+        <v>-4.7436373117497332</v>
       </c>
       <c r="B19">
-        <v>3.0915490295451606</v>
+        <v>3.2314530008815177</v>
       </c>
       <c r="C19">
         <v>258.22826917492205</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-4.8953585212057122</v>
+        <v>-5.1065687819395356</v>
       </c>
       <c r="B20">
-        <v>2.5646738209508486</v>
+        <v>2.7029373015409539</v>
       </c>
       <c r="C20">
         <v>258.22826917492205</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-5.24750255441548</v>
+        <v>-5.4554682382188942</v>
       </c>
       <c r="B21">
-        <v>2.0289201210768777</v>
+        <v>2.1650114767752449</v>
       </c>
       <c r="C21">
         <v>258.22826917492205</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-5.5871711096588017</v>
+        <v>-5.791294382300296</v>
       </c>
       <c r="B22">
-        <v>1.4847908984934639</v>
+        <v>1.6183184495046052</v>
       </c>
       <c r="C22">
         <v>258.22826917492205</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-5.9144464472320344</v>
+        <v>-6.1141575759537385</v>
       </c>
       <c r="B23">
-        <v>0.93234137937967843</v>
+        <v>1.0629322303524857</v>
       </c>
       <c r="C23">
         <v>258.22826917492205</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-6.2292440975291372</v>
+        <v>-6.4239560959635886</v>
       </c>
       <c r="B24">
-        <v>0.37151485431681336</v>
+        <v>0.4987846018681486</v>
       </c>
       <c r="C24">
         <v>258.22826917492205</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-6.5314795909440742</v>
+        <v>-6.7205882191142221</v>
       </c>
       <c r="B25">
-        <v>-0.19774538611384754</v>
+        <v>-0.074192653399147129</v>
       </c>
       <c r="C25">
         <v>258.22826917492205</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-6.8210341404290249</v>
+        <v>-7.0039104520358153</v>
       </c>
       <c r="B26">
-        <v>-0.77551909064972224</v>
+        <v>-0.656095764730262</v>
       </c>
       <c r="C26">
         <v>258.22826917492205</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-7.0976516891690622</v>
+        <v>-7.2736122207417866</v>
       </c>
       <c r="B27">
-        <v>-1.3619781653030845</v>
+        <v>-1.2471330087265637</v>
       </c>
       <c r="C27">
         <v>258.22826917492205</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-7.361041862907479</v>
+        <v>-7.5293411810913611</v>
       </c>
       <c r="B28">
-        <v>-1.9573175554049114</v>
+        <v>-1.8475406738195392</v>
       </c>
       <c r="C28">
         <v>258.22826917492205</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-7.6109142873875664</v>
+        <v>-7.770744988943763</v>
       </c>
       <c r="B29">
-        <v>-2.5617322062861847</v>
+        <v>-2.457555048440677</v>
       </c>
       <c r="C29">
         <v>258.22826917492205</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-7.8470874065798144</v>
+        <v>-7.997613952767388</v>
       </c>
       <c r="B30">
-        <v>-3.1753440071965389</v>
+        <v>-3.0773167555700791</v>
       </c>
       <c r="C30">
         <v>258.22826917492205</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-8.069814937363498</v>
+        <v>-8.2103089914673255</v>
       </c>
       <c r="B31">
-        <v>-3.7979826230602405</v>
+        <v>-3.70658375638232</v>
       </c>
       <c r="C31">
         <v>258.22826917492205</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-8.2794594148451</v>
+        <v>-8.4093336765578428</v>
       </c>
       <c r="B32">
-        <v>-4.4294046627202279</v>
+        <v>-4.3450183466006029</v>
       </c>
       <c r="C32">
         <v>258.22826917492205</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-8.4763833741310979</v>
+        <v>-8.5951915795532</v>
       </c>
       <c r="B33">
-        <v>-5.0693667350194263</v>
+        <v>-4.9922828219481215</v>
       </c>
       <c r="C33">
         <v>258.22826917492205</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-8.6607462666940282</v>
+        <v>-8.7681285828266962</v>
       </c>
       <c r="B34">
-        <v>-5.7177617907984439</v>
+        <v>-5.6482122892037427</v>
       </c>
       <c r="C34">
         <v>258.22826917492205</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-8.8318952094706571</v>
+        <v>-8.9273598121877882</v>
       </c>
       <c r="B35">
-        <v>-6.3750281488886236</v>
+        <v>-6.3133330993690535</v>
       </c>
       <c r="C35">
         <v>258.22826917492205</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-8.988974235763818</v>
+        <v>-9.0718427043049665</v>
       </c>
       <c r="B36">
-        <v>-7.04174047011899</v>
+        <v>-6.9883444145013174</v>
       </c>
       <c r="C36">
         <v>258.22826917492205</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-9.13112737887634</v>
+        <v>-9.20053469584672</v>
       </c>
       <c r="B37">
-        <v>-7.71847341531857</v>
+        <v>-7.6739453966577962</v>
       </c>
       <c r="C37">
         <v>258.22826917492205</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-9.257016327693453</v>
+        <v>-9.31177692308037</v>
       </c>
       <c r="B38">
-        <v>-8.4061254715164129</v>
+        <v>-8.3712485102279484</v>
       </c>
       <c r="C38">
         <v>258.22826917492205</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-9.3633733934299972</v>
+        <v>-9.4014453206685324</v>
       </c>
       <c r="B39">
-        <v>-9.1068904305416645</v>
+        <v>-9.08301942893002</v>
       </c>
       <c r="C39">
         <v>258.22826917492205</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-9.44644854288322</v>
+        <v>-9.4647995228726618</v>
       </c>
       <c r="B40">
-        <v>-9.8232859104235022</v>
+        <v>-9.8124371288144712</v>
       </c>
       <c r="C40">
         <v>258.22826917492205</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-9.5024917428503581</v>
+        <v>-9.4970991639541964</v>
       </c>
       <c r="B41">
-        <v>-10.557829529191084</v>
+        <v>-10.562680585931732</v>
       </c>
       <c r="C41">
         <v>258.22826917492205</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-9.5024917428503581</v>
+        <v>-9.4970991639541964</v>
       </c>
       <c r="B42">
-        <v>-10.557829529191084</v>
+        <v>-10.562680585931732</v>
       </c>
       <c r="C42">
         <v>258.22826917492205</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-9.282925376146812</v>
+        <v>-9.254483401126441</v>
       </c>
       <c r="B43">
-        <v>-9.9330686378031352</v>
+        <v>-9.9534789705054312</v>
       </c>
       <c r="C43">
         <v>258.22826917492205</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-9.06441087057651</v>
+        <v>-9.0169332077434827</v>
       </c>
       <c r="B44">
-        <v>-9.3076015701201786</v>
+        <v>-9.34088029146947</v>
       </c>
       <c r="C44">
         <v>258.22826917492205</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-8.8437772992937678</v>
+        <v>-8.780287522882448</v>
       </c>
       <c r="B45">
-        <v>-8.68355715598566</v>
+        <v>-8.727675032459052</v>
       </c>
       <c r="C45">
         <v>258.22826917492205</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-8.6178537354529023</v>
+        <v>-8.540385285620463</v>
       </c>
       <c r="B46">
-        <v>-8.063064225243</v>
+        <v>-8.1166536771093725</v>
       </c>
       <c r="C46">
         <v>258.22826917492205</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-8.3839231217476371</v>
+        <v>-8.2936532507993448</v>
       </c>
       <c r="B47">
-        <v>-7.4479468983974666</v>
+        <v>-7.5102125090421383</v>
       </c>
       <c r="C47">
         <v>258.22826917492205</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-8.1410838790293329</v>
+        <v>-8.0388694363197271</v>
       </c>
       <c r="B48">
-        <v>-6.8388104586016638</v>
+        <v>-6.9091710118251282</v>
       </c>
       <c r="C48">
         <v>258.22826917492205</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-7.888888297688764</v>
+        <v>-7.7753996758469448</v>
       </c>
       <c r="B49">
-        <v>-6.2359554796700287</v>
+        <v>-6.313954469012625</v>
       </c>
       <c r="C49">
         <v>258.22826917492205</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-7.6268886681167016</v>
+        <v>-7.5026098030463242</v>
       </c>
       <c r="B50">
-        <v>-5.6396825354170019</v>
+        <v>-5.7249881641589164</v>
       </c>
       <c r="C50">
         <v>258.22826917492205</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-7.3548158176639733</v>
+        <v>-7.2200987856381786</v>
       </c>
       <c r="B51">
-        <v>-5.0501723372864182</v>
+        <v>-5.1425410368528182</v>
       </c>
       <c r="C51">
         <v>258.22826917492205</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-7.0731147215216463</v>
+        <v>-6.9283981275627546</v>
       </c>
       <c r="B52">
-        <v>-4.467126147239715</v>
+        <v>-4.5662566508212867</v>
       </c>
       <c r="C52">
         <v>258.22826917492205</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-6.7824088918408387</v>
+        <v>-6.6282724668152735</v>
       </c>
       <c r="B53">
-        <v>-3.8901253648677292</v>
+        <v>-3.9956222258258052</v>
       </c>
       <c r="C53">
         <v>258.22826917492205</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-6.4833218407726667</v>
+        <v>-6.3204864413909538</v>
       </c>
       <c r="B54">
-        <v>-3.3187513897612817</v>
+        <v>-3.4301249816278472</v>
       </c>
       <c r="C54">
         <v>258.22826917492205</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-6.176349400111758</v>
+        <v>-6.0056431680825355</v>
       </c>
       <c r="B55">
-        <v>-2.7526713408502377</v>
+        <v>-2.8693604570643991</v>
       </c>
       <c r="C55">
         <v>258.22826917492205</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-5.8614766802267715</v>
+        <v>-5.6836996788728325</v>
       </c>
       <c r="B56">
-        <v>-2.1918952144205783</v>
+        <v>-2.3133574672744461</v>
       </c>
       <c r="C56">
         <v>258.22826917492205</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-5.5385611111298685</v>
+        <v>-5.35445148454217</v>
       </c>
       <c r="B57">
-        <v>-1.6365187260973091</v>
+        <v>-1.7622531464724702</v>
       </c>
       <c r="C57">
         <v>258.22826917492205</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-5.2074601228332122</v>
+        <v>-5.0176940958708736</v>
       </c>
       <c r="B58">
-        <v>-1.0866375915054367</v>
+        <v>-1.2161846288729548</v>
       </c>
       <c r="C58">
         <v>258.22826917492205</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-4.8680488967265578</v>
+        <v>-4.6732482220521181</v>
       </c>
       <c r="B59">
-        <v>-0.54233560872527642</v>
+        <v>-0.67527215017339015</v>
       </c>
       <c r="C59">
         <v>258.22826917492205</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-4.5202736197100384</v>
+        <v>-4.3210353659304781</v>
       </c>
       <c r="B60">
-        <v>-0.0036489056584034993</v>
+        <v>-0.1395683520033302</v>
       </c>
       <c r="C60">
         <v>258.22826917492205</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-4.1640982300613789</v>
+        <v>-3.9610022287633737</v>
       </c>
       <c r="B61">
-        <v>0.52939830733830406</v>
+        <v>0.39089102252466723</v>
       </c>
       <c r="C61">
         <v>258.22826917492205</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-3.7994866660583062</v>
+        <v>-3.5930955118082268</v>
       </c>
       <c r="B62">
-        <v>1.0567818199079586</v>
+        <v>0.91607023029803736</v>
       </c>
       <c r="C62">
         <v>258.22826917492205</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-3.4265531130653208</v>
+        <v>-3.2174575128438376</v>
       </c>
       <c r="B63">
-        <v>1.5785782914071052</v>
+        <v>1.4360646988124191</v>
       </c>
       <c r="C63">
         <v>258.22826917492205</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-3.0460127447940204</v>
+        <v>-2.8350129157345103</v>
       </c>
       <c r="B64">
-        <v>2.0952678600459822</v>
+        <v>1.951494537996241</v>
       </c>
       <c r="C64">
         <v>258.22826917492205</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.6587309820427802</v>
+        <v>-2.446882000865926</v>
       </c>
       <c r="B65">
-        <v>2.6074315337482545</v>
+        <v>2.4631110283861304</v>
       </c>
       <c r="C65">
         <v>258.22826917492205</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.2655732456099726</v>
+        <v>-2.0541850486237672</v>
       </c>
       <c r="B66">
-        <v>3.1156503204375867</v>
+        <v>2.9716654505187146</v>
       </c>
       <c r="C66">
         <v>258.22826917492205</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.8662477254734073</v>
+        <v>-1.6565559125460183</v>
       </c>
       <c r="B67">
-        <v>3.6197283108691178</v>
+        <v>3.476912259873191</v>
       </c>
       <c r="C67">
         <v>258.22826917492205</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-1.4558336883286407</v>
+        <v>-1.2476827387798684</v>
       </c>
       <c r="B68">
-        <v>4.1163619271238767</v>
+        <v>3.9746186116990292</v>
       </c>
       <c r="C68">
         <v>258.22826917492205</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-1.0304965354707989</v>
+        <v>-0.822653512017381</v>
       </c>
       <c r="B69">
-        <v>4.6029767773733061</v>
+        <v>4.4614904186020148</v>
       </c>
       <c r="C69">
         <v>258.22826917492205</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-0.59537512987559249</v>
+        <v>-0.38810127852091819</v>
       </c>
       <c r="B70">
-        <v>5.083022882824566</v>
+        <v>4.9419759228428743</v>
       </c>
       <c r="C70">
         <v>258.22826917492205</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-0.15607137734819113</v>
+        <v>0.048742977536676661</v>
       </c>
       <c r="B71">
-        <v>5.5602611325925766</v>
+        <v>5.4209243547921062</v>
       </c>
       <c r="C71">
         <v>258.22826917492205</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>0.28893410666892916</v>
+        <v>0.48980158191090684</v>
       </c>
       <c r="B72">
-        <v>6.0336714743875426</v>
+        <v>5.8970465676043071</v>
       </c>
       <c r="C72">
         <v>258.22826917492205</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>0.74211574856404</v>
+        <v>0.93822226239990547</v>
       </c>
       <c r="B73">
-        <v>6.501592680121564</v>
+        <v>6.3682316373897381</v>
       </c>
       <c r="C73">
         <v>258.22826917492205</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>1.2026468516857127</v>
+        <v>1.3929010450439727</v>
       </c>
       <c r="B74">
-        <v>6.9645797599190251</v>
+        <v>6.8352199092972317</v>
       </c>
       <c r="C74">
         <v>258.22826917492205</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>1.6688630972194183</v>
+        <v>1.8516534817648267</v>
       </c>
       <c r="B75">
-        <v>7.4237500689677844</v>
+        <v>7.299476314200751</v>
       </c>
       <c r="C75">
         <v>258.22826917492205</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>2.1390508007379547</v>
+        <v>2.3122249297676976</v>
       </c>
       <c r="B76">
-        <v>7.8802541044973236</v>
+        <v>7.7625128568362625</v>
       </c>
       <c r="C76">
         <v>258.22826917492205</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>2.6116491415162613</v>
+        <v>2.7725536544394287</v>
       </c>
       <c r="B77">
-        <v>8.33513973733578</v>
+        <v>8.22571217418139</v>
       </c>
       <c r="C77">
         <v>258.22826917492205</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>3.085758119250547</v>
+        <v>3.2314197486098113</v>
       </c>
       <c r="B78">
-        <v>8.7890111906642758</v>
+        <v>8.6898923583184278</v>
       </c>
       <c r="C78">
         <v>258.22826917492205</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>3.5597049855432266</v>
+        <v>3.6866055641187714</v>
       </c>
       <c r="B79">
-        <v>9.2429914789459726</v>
+        <v>9.1565406047040145</v>
       </c>
       <c r="C79">
         <v>258.22826917492205</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>4.0304111477003666</v>
+        <v>4.1340770079294353</v>
       </c>
       <c r="B80">
-        <v>9.6991474426731177</v>
+        <v>9.628362249984475</v>
       </c>
       <c r="C80">
         <v>258.22826917492205</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>4.489965229962614</v>
+        <v>4.5635772251277738</v>
       </c>
       <c r="B81">
-        <v>10.162790454084398</v>
+        <v>10.1122357288467</v>
       </c>
       <c r="C81">
         <v>258.22826917492205</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>4.79113733979563</v>
+        <v>4.78565604483323</v>
       </c>
       <c r="B82">
-        <v>10.732764606508106</v>
+        <v>10.735209794319259</v>
       </c>
       <c r="C82">
         <v>258.22826917492205</v>
